--- a/automation/reports/Excel/Failed_Test_Cases.xlsx
+++ b/automation/reports/Excel/Failed_Test_Cases.xlsx
@@ -428,82 +428,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Test Case ID</t>
+          <t>Test ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Title / Test Name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
           <t>Duration (s)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Error Message</t>
         </is>
       </c>
     </row>
